--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0980D7-FA60-45E5-A7C6-DA9FF50C4963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB7895E-DDB7-404D-9452-699882CC5438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -410,29 +413,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -453,7 +456,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -477,7 +480,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -485,20 +488,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -510,17 +513,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -538,7 +541,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -839,6 +842,9 @@
                 <c:pt idx="39">
                   <c:v>3867.57</c:v>
                 </c:pt>
+                <c:pt idx="40">
+                  <c:v>4049.2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1131,6 +1137,9 @@
                   <c:v>3229.87</c:v>
                 </c:pt>
                 <c:pt idx="39">
+                  <c:v>3194.62</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>3194.62</c:v>
                 </c:pt>
               </c:numCache>
@@ -1192,8 +1201,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -1253,8 +1262,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -1295,8 +1304,8 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
@@ -1306,7 +1315,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1314,6 +1322,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1330,7 +1339,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ko-KR"/>
     </a:p>
@@ -2206,19 +2218,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
   <dimension ref="A1:Y42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="3"/>
     <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1">
+    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>114</v>
       </c>
@@ -2257,7 +2269,7 @@
       <c r="X1" s="8"/>
       <c r="Y1" s="8"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45825</v>
       </c>
@@ -2296,7 +2308,7 @@
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45832</v>
       </c>
@@ -2335,7 +2347,7 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45839</v>
       </c>
@@ -2355,7 +2367,7 @@
         <v>677.73</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45846</v>
       </c>
@@ -2375,7 +2387,7 @@
         <v>676.06</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45853</v>
       </c>
@@ -2395,7 +2407,7 @@
         <v>676.1</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45860</v>
       </c>
@@ -2415,7 +2427,7 @@
         <v>674.57</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45867</v>
       </c>
@@ -2435,7 +2447,7 @@
         <v>681.42</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45874</v>
       </c>
@@ -2455,7 +2467,7 @@
         <v>681.58</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45881</v>
       </c>
@@ -2475,7 +2487,7 @@
         <v>681.87</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45888</v>
       </c>
@@ -2495,7 +2507,7 @@
         <v>682.04</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45895</v>
       </c>
@@ -2515,7 +2527,7 @@
         <v>681.5</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45902</v>
       </c>
@@ -2535,7 +2547,7 @@
         <v>679.81</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45909</v>
       </c>
@@ -2555,7 +2567,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45916</v>
       </c>
@@ -2575,7 +2587,7 @@
         <v>689.45</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45923</v>
       </c>
@@ -2595,7 +2607,7 @@
         <v>711.44</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45930</v>
       </c>
@@ -2615,7 +2627,7 @@
         <v>717.66</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45944</v>
       </c>
@@ -2635,7 +2647,7 @@
         <v>794.72</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45951</v>
       </c>
@@ -2655,7 +2667,7 @@
         <v>824.91</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45958</v>
       </c>
@@ -2675,7 +2687,7 @@
         <v>930.72</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>45965</v>
       </c>
@@ -2695,7 +2707,7 @@
         <v>1015.38</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>45972</v>
       </c>
@@ -2715,7 +2727,7 @@
         <v>1054.43</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>45979</v>
       </c>
@@ -2735,7 +2747,7 @@
         <v>1217.8800000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>45986</v>
       </c>
@@ -2755,7 +2767,7 @@
         <v>1438.48</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>45993</v>
       </c>
@@ -2775,7 +2787,7 @@
         <v>1633.81</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>46000</v>
       </c>
@@ -2795,7 +2807,7 @@
         <v>1735.53</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>46007</v>
       </c>
@@ -2815,7 +2827,7 @@
         <v>1742.09</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46014</v>
       </c>
@@ -2835,7 +2847,7 @@
         <v>1860.57</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>46021</v>
       </c>
@@ -2855,7 +2867,7 @@
         <v>1896.1</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>46028</v>
       </c>
@@ -2875,7 +2887,7 @@
         <v>1982.64</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>46035</v>
       </c>
@@ -2895,7 +2907,7 @@
         <v>2011.73</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>46042</v>
       </c>
@@ -2915,7 +2927,7 @@
         <v>2229.8200000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>46049</v>
       </c>
@@ -2935,7 +2947,7 @@
         <v>2521.86</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>46056</v>
       </c>
@@ -2955,7 +2967,7 @@
         <v>2567.14</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>46063</v>
       </c>
@@ -2975,7 +2987,7 @@
         <v>2605.37</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>46077</v>
       </c>
@@ -2995,7 +3007,7 @@
         <v>2750.87</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>46084</v>
       </c>
@@ -3015,7 +3027,7 @@
         <v>2901.01</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>46091</v>
       </c>
@@ -3035,7 +3047,7 @@
         <v>3046.26</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>46098</v>
       </c>
@@ -3055,7 +3067,7 @@
         <v>3198.66</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>46105</v>
       </c>
@@ -3075,7 +3087,7 @@
         <v>3229.87</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>46112</v>
       </c>
@@ -3095,7 +3107,7 @@
         <v>3194.62</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>46119</v>
       </c>
@@ -3107,6 +3119,12 @@
       </c>
       <c r="D42" s="4" t="s">
         <v>116</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4049.2</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3194.62</v>
       </c>
     </row>
   </sheetData>
@@ -3119,20 +3137,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3143,22 +3161,22 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="2:5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
@@ -3166,42 +3184,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:5">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
@@ -3209,32 +3227,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -3242,37 +3260,37 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="2:3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="2:3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
@@ -3280,17 +3298,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="2:3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
@@ -3298,47 +3316,47 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="2:3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="2:3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="2:3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="2:3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C36" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="2:3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="2:3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="2:3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>44</v>
       </c>
@@ -3346,47 +3364,47 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="2:3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="2:3">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="2:3">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="2:3">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:3">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="2:3">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="2:3">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="2:3">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="2:3">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>54</v>
       </c>
@@ -3394,27 +3412,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="2:3">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="2:3">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:3">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="2:3">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="2:3">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>60</v>
       </c>
@@ -3422,32 +3440,32 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="2:3">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="2:3">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="2:3">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="2:3">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="2:3">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="2:3">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
@@ -3455,17 +3473,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="2:3">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="2:3">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="2:3">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
@@ -3473,22 +3491,22 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="2:3">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="64" spans="2:3">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="2:3">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="2:3">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
         <v>76</v>
       </c>
@@ -3496,22 +3514,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67" spans="2:3">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="2:3">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="2:3">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="2:3">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
         <v>81</v>
       </c>
@@ -3519,47 +3537,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="2:3">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="2:3">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="2:3">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="2:3">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="2:3">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="2:3">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="2:3">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="78" spans="2:3">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C78" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="2:3">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
         <v>91</v>
       </c>
@@ -3567,32 +3585,32 @@
         <v>92</v>
       </c>
     </row>
-    <row r="80" spans="2:3">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="2:3">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="82" spans="2:3">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="2:3">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="2:3">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="2:3">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B85" s="2" t="s">
         <v>98</v>
       </c>
@@ -3600,47 +3618,47 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="2:3">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="2:3">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="2:3">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="2:3">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="2:3">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="2:3">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="2:3">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="2:3">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="94" spans="2:3">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>108</v>
       </c>
@@ -3654,7 +3672,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF528F66-5C7C-40F6-B437-A79684695F91}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="14"/>
   </cols>

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB7895E-DDB7-404D-9452-699882CC5438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A0BB0E-5B94-454D-A395-073D20BA77B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -22,15 +22,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -713,6 +710,12 @@
                 <c:pt idx="40">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -844,6 +847,12 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>4049.2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3991.58</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3977.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1010,6 +1019,12 @@
                 <c:pt idx="40">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="41">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1141,6 +1156,12 @@
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>3194.62</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3164.63</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3142.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1315,6 +1336,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1322,7 +1344,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2217,15 +2238,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y44"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="3"/>
     <col min="26" max="16384" width="9" style="1"/>
   </cols>
@@ -3127,6 +3148,46 @@
         <v>3194.62</v>
       </c>
     </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B43" s="6">
+        <v>46126</v>
+      </c>
+      <c r="C43" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3991.58</v>
+      </c>
+      <c r="F43" s="3">
+        <v>3164.63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B44" s="6">
+        <v>46133</v>
+      </c>
+      <c r="C44" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3977.5</v>
+      </c>
+      <c r="F44" s="3">
+        <v>3142.68</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3137,11 +3198,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.8984375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3672,7 +3733,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF528F66-5C7C-40F6-B437-A79684695F91}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="9" style="14"/>
   </cols>

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF1461C-EB31-4A6B-875E-EAE841569C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC70A253-C80E-4B44-82E5-88CA06D60BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32415" yWindow="1860" windowWidth="21600" windowHeight="10875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -415,7 +415,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,6 +457,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -481,46 +489,48 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -538,7 +548,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -731,6 +741,9 @@
                 <c:pt idx="47">
                   <c:v>46175</c:v>
                 </c:pt>
+                <c:pt idx="48">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -883,6 +896,9 @@
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>3913.14</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3945.05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1070,6 +1086,9 @@
                 <c:pt idx="47">
                   <c:v>46175</c:v>
                 </c:pt>
+                <c:pt idx="48">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1221,6 +1240,9 @@
                   <c:v>3014.54</c:v>
                 </c:pt>
                 <c:pt idx="47">
+                  <c:v>3014.38</c:v>
+                </c:pt>
+                <c:pt idx="48">
                   <c:v>3014.38</c:v>
                 </c:pt>
               </c:numCache>
@@ -2298,1053 +2320,1073 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:Y50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="25" width="9" style="3"/>
-    <col min="26" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.90625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.54296875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="25" width="9" style="16"/>
+    <col min="26" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:25" s="10" customFormat="1">
+      <c r="A1" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="6">
+      <c r="A2" s="11">
         <v>45825</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>45825</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="14">
         <v>678.45</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="14">
         <v>674.2</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="6">
+      <c r="A3" s="11">
         <v>45832</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="11">
         <v>45832</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="14">
         <v>702.26</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="14">
         <v>673.9</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="6">
+      <c r="A4" s="11">
         <v>45839</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="11">
         <v>45839</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="16">
         <v>731.64</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="16">
         <v>677.73</v>
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="6">
+      <c r="A5" s="11">
         <v>45846</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="11">
         <v>45846</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="16">
         <v>789.39</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="16">
         <v>676.06</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="6">
+      <c r="A6" s="11">
         <v>45853</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="11">
         <v>45853</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="16">
         <v>790.1</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="16">
         <v>676.1</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="6">
+      <c r="A7" s="11">
         <v>45860</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="11">
         <v>45860</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="16">
         <v>808</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="16">
         <v>674.57</v>
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="6">
+      <c r="A8" s="11">
         <v>45867</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="11">
         <v>45867</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="16">
         <v>823.54</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="16">
         <v>681.42</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="6">
+      <c r="A9" s="11">
         <v>45874</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="11">
         <v>45874</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="16">
         <v>823.06</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="16">
         <v>681.58</v>
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="6">
+      <c r="A10" s="11">
         <v>45881</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="11">
         <v>45881</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="16">
         <v>837.73</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="16">
         <v>681.87</v>
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="6">
+      <c r="A11" s="11">
         <v>45888</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="11">
         <v>45888</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="16">
         <v>837.73</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="16">
         <v>682.04</v>
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="6">
+      <c r="A12" s="11">
         <v>45895</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="11">
         <v>45895</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="16">
         <v>848.95</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="16">
         <v>681.5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="6">
+      <c r="A13" s="11">
         <v>45902</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="11">
         <v>45902</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="16">
         <v>850.22</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="16">
         <v>679.81</v>
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="6">
+      <c r="A14" s="11">
         <v>45909</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="11">
         <v>45909</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="16">
         <v>856.43</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="16">
         <v>676.9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="6">
+      <c r="A15" s="11">
         <v>45916</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="11">
         <v>45916</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="16">
         <v>859.16</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="16">
         <v>689.45</v>
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="6">
+      <c r="A16" s="11">
         <v>45923</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="11">
         <v>45923</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="16">
         <v>872.12</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="16">
         <v>711.44</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="6">
+      <c r="A17" s="11">
         <v>45930</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="11">
         <v>45930</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="16">
         <v>902.19</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="16">
         <v>717.66</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="6">
+      <c r="A18" s="11">
         <v>45944</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="11">
         <v>45944</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="16">
         <v>1060.18</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="16">
         <v>794.72</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="6">
+      <c r="A19" s="11">
         <v>45951</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="11">
         <v>45951</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="16">
         <v>1105.6400000000001</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="16">
         <v>824.91</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="6">
+      <c r="A20" s="11">
         <v>45958</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="11">
         <v>45958</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="16">
         <v>1208.73</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="16">
         <v>930.72</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="6">
+      <c r="A21" s="11">
         <v>45965</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="11">
         <v>45965</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="16">
         <v>1319.21</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="16">
         <v>1015.38</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="6">
+      <c r="A22" s="11">
         <v>45972</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="11">
         <v>45972</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="16">
         <v>1520.48</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="16">
         <v>1054.43</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="6">
+      <c r="A23" s="11">
         <v>45979</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="11">
         <v>45979</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="16">
         <v>1709.71</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="16">
         <v>1217.8800000000001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="6">
+      <c r="A24" s="11">
         <v>45986</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="11">
         <v>45986</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="16">
         <v>1909.52</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="16">
         <v>1438.48</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="6">
+      <c r="A25" s="11">
         <v>45993</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="11">
         <v>45993</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="16">
         <v>2000.37</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="16">
         <v>1633.81</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="6">
+      <c r="A26" s="11">
         <v>46000</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="11">
         <v>46000</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="16">
         <v>2191.25</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="16">
         <v>1735.53</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="6">
+      <c r="A27" s="11">
         <v>46007</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="11">
         <v>46007</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="16">
         <v>2217.7399999999998</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="16">
         <v>1742.09</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="6">
+      <c r="A28" s="11">
         <v>46014</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="11">
         <v>46014</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="16">
         <v>2217.7399999999998</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="16">
         <v>1860.57</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="6">
+      <c r="A29" s="11">
         <v>46021</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="11">
         <v>46021</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="16">
         <v>2309.29</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="16">
         <v>1896.1</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="6">
+      <c r="A30" s="11">
         <v>46028</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="11">
         <v>46028</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="16">
         <v>2561.1999999999998</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="16">
         <v>1982.64</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="6">
+      <c r="A31" s="11">
         <v>46035</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="11">
         <v>46035</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="16">
         <v>2987.1</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="16">
         <v>2011.73</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="6">
+      <c r="A32" s="11">
         <v>46042</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="11">
         <v>46042</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="12">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="16">
         <v>3077.44</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="16">
         <v>2229.8200000000002</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="6">
+      <c r="A33" s="11">
         <v>46049</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="11">
         <v>46049</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="16">
         <v>3132.82</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="16">
         <v>2521.86</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="6">
+      <c r="A34" s="11">
         <v>46056</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="11">
         <v>46056</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="16">
         <v>3213.44</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="16">
         <v>2567.14</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="6">
+      <c r="A35" s="11">
         <v>46063</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="11">
         <v>46063</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="16">
         <v>3406.87</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="16">
         <v>2605.37</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="6">
+      <c r="A36" s="11">
         <v>46077</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="11">
         <v>46077</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="16">
         <v>3406.87</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="16">
         <v>2750.87</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="6">
+      <c r="A37" s="11">
         <v>46084</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="11">
         <v>46084</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="16">
         <v>3633.16</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="16">
         <v>2901.01</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="6">
+      <c r="A38" s="11">
         <v>46091</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="11">
         <v>46091</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="16">
         <v>3811.51</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="16">
         <v>3046.26</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="6">
+      <c r="A39" s="11">
         <v>46098</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="11">
         <v>46098</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="16">
         <v>3968.8</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="16">
         <v>3198.66</v>
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="6">
+      <c r="A40" s="11">
         <v>46105</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40" s="11">
         <v>46105</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="16">
         <v>3968.8</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="16">
         <v>3229.87</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="6">
+      <c r="A41" s="11">
         <v>46112</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="11">
         <v>46112</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="16">
         <v>3867.57</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="16">
         <v>3194.62</v>
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="6">
+      <c r="A42" s="11">
         <v>46119</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="11">
         <v>46119</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="16">
         <v>4049.2</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="16">
         <v>3194.62</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="6">
+      <c r="A43" s="11">
         <v>46126</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="11">
         <v>46126</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="16">
         <v>3991.58</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="16">
         <v>3164.63</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="6">
+      <c r="A44" s="11">
         <v>46133</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="11">
         <v>46133</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="16">
         <v>3977.5</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="16">
         <v>3142.68</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="6">
+      <c r="A45" s="11">
         <v>46140</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="11">
         <v>46140</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="16">
         <v>3938.46</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="16">
         <v>3059.92</v>
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="6">
+      <c r="A46" s="11">
         <v>46154</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="11">
         <v>46154</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="16">
         <v>3945.39</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="16">
         <v>3029.7</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="6">
+      <c r="A47" s="11">
         <v>46161</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="11">
         <v>46161</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="16">
         <v>3932.44</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="16">
         <v>3019.44</v>
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="6">
+      <c r="A48" s="11">
         <v>46168</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="11">
         <v>46168</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="16">
         <v>3913.14</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="16">
         <v>3014.54</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="6">
+      <c r="A49" s="11">
         <v>46175</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="11">
         <v>46175</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="16">
         <v>3913.14</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="16">
+        <v>3014.38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="11">
+        <v>46182</v>
+      </c>
+      <c r="B50" s="11">
+        <v>46182</v>
+      </c>
+      <c r="C50" s="12">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="16">
+        <v>3945.05</v>
+      </c>
+      <c r="F50" s="16">
         <v>3014.38</v>
       </c>
     </row>
@@ -3358,11 +3400,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3893,9 +3935,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF528F66-5C7C-40F6-B437-A79684695F91}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="16384" width="9" style="14"/>
+    <col min="1" max="16384" width="9" style="3"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC70A253-C80E-4B44-82E5-88CA06D60BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D38588AE-B2BB-4E3B-8FE7-0F9F6023415E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -489,7 +489,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -506,31 +506,30 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -548,7 +547,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -744,6 +743,9 @@
                 <c:pt idx="48">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="49">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -899,6 +901,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>3945.05</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3974.13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1089,6 +1094,9 @@
                 <c:pt idx="48">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="49">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1244,6 +1252,9 @@
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>3014.38</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3015.97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2320,17 +2331,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Y51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.90625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.54296875" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="25" width="9" style="16"/>
-    <col min="26" max="16384" width="9" style="15"/>
+    <col min="1" max="2" width="11.6640625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="25" width="9" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="10" customFormat="1">
@@ -2463,10 +2473,10 @@
       <c r="D4" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="15">
         <v>731.64</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="15">
         <v>677.73</v>
       </c>
     </row>
@@ -2483,10 +2493,10 @@
       <c r="D5" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>789.39</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>676.06</v>
       </c>
     </row>
@@ -2503,10 +2513,10 @@
       <c r="D6" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="15">
         <v>790.1</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="15">
         <v>676.1</v>
       </c>
     </row>
@@ -2523,10 +2533,10 @@
       <c r="D7" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>808</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>674.57</v>
       </c>
     </row>
@@ -2543,10 +2553,10 @@
       <c r="D8" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>823.54</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>681.42</v>
       </c>
     </row>
@@ -2563,10 +2573,10 @@
       <c r="D9" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>823.06</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>681.58</v>
       </c>
     </row>
@@ -2583,10 +2593,10 @@
       <c r="D10" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <v>837.73</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>681.87</v>
       </c>
     </row>
@@ -2603,10 +2613,10 @@
       <c r="D11" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>837.73</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>682.04</v>
       </c>
     </row>
@@ -2623,10 +2633,10 @@
       <c r="D12" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>848.95</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>681.5</v>
       </c>
     </row>
@@ -2643,10 +2653,10 @@
       <c r="D13" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <v>850.22</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <v>679.81</v>
       </c>
     </row>
@@ -2663,10 +2673,10 @@
       <c r="D14" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="15">
         <v>856.43</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>676.9</v>
       </c>
     </row>
@@ -2683,10 +2693,10 @@
       <c r="D15" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <v>859.16</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>689.45</v>
       </c>
     </row>
@@ -2703,10 +2713,10 @@
       <c r="D16" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>872.12</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>711.44</v>
       </c>
     </row>
@@ -2723,10 +2733,10 @@
       <c r="D17" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="15">
         <v>902.19</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="15">
         <v>717.66</v>
       </c>
     </row>
@@ -2743,10 +2753,10 @@
       <c r="D18" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>1060.18</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>794.72</v>
       </c>
     </row>
@@ -2763,10 +2773,10 @@
       <c r="D19" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>1105.6400000000001</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>824.91</v>
       </c>
     </row>
@@ -2783,10 +2793,10 @@
       <c r="D20" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>1208.73</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>930.72</v>
       </c>
     </row>
@@ -2803,10 +2813,10 @@
       <c r="D21" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="15">
         <v>1319.21</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="15">
         <v>1015.38</v>
       </c>
     </row>
@@ -2823,10 +2833,10 @@
       <c r="D22" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="15">
         <v>1520.48</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="15">
         <v>1054.43</v>
       </c>
     </row>
@@ -2843,10 +2853,10 @@
       <c r="D23" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="15">
         <v>1709.71</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="15">
         <v>1217.8800000000001</v>
       </c>
     </row>
@@ -2863,10 +2873,10 @@
       <c r="D24" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="15">
         <v>1909.52</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <v>1438.48</v>
       </c>
     </row>
@@ -2883,10 +2893,10 @@
       <c r="D25" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="15">
         <v>2000.37</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="15">
         <v>1633.81</v>
       </c>
     </row>
@@ -2903,10 +2913,10 @@
       <c r="D26" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="15">
         <v>2191.25</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="15">
         <v>1735.53</v>
       </c>
     </row>
@@ -2923,10 +2933,10 @@
       <c r="D27" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="15">
         <v>2217.7399999999998</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="15">
         <v>1742.09</v>
       </c>
     </row>
@@ -2943,10 +2953,10 @@
       <c r="D28" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="15">
         <v>2217.7399999999998</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="15">
         <v>1860.57</v>
       </c>
     </row>
@@ -2963,10 +2973,10 @@
       <c r="D29" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="15">
         <v>2309.29</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="15">
         <v>1896.1</v>
       </c>
     </row>
@@ -2983,10 +2993,10 @@
       <c r="D30" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="15">
         <v>2561.1999999999998</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="15">
         <v>1982.64</v>
       </c>
     </row>
@@ -3003,10 +3013,10 @@
       <c r="D31" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="15">
         <v>2987.1</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="15">
         <v>2011.73</v>
       </c>
     </row>
@@ -3023,10 +3033,10 @@
       <c r="D32" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="15">
         <v>3077.44</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="15">
         <v>2229.8200000000002</v>
       </c>
     </row>
@@ -3043,10 +3053,10 @@
       <c r="D33" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="15">
         <v>3132.82</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="15">
         <v>2521.86</v>
       </c>
     </row>
@@ -3063,10 +3073,10 @@
       <c r="D34" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="15">
         <v>3213.44</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="15">
         <v>2567.14</v>
       </c>
     </row>
@@ -3083,10 +3093,10 @@
       <c r="D35" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="15">
         <v>3406.87</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="15">
         <v>2605.37</v>
       </c>
     </row>
@@ -3103,10 +3113,10 @@
       <c r="D36" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="15">
         <v>3406.87</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="15">
         <v>2750.87</v>
       </c>
     </row>
@@ -3123,10 +3133,10 @@
       <c r="D37" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="15">
         <v>3633.16</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="15">
         <v>2901.01</v>
       </c>
     </row>
@@ -3143,10 +3153,10 @@
       <c r="D38" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="15">
         <v>3811.51</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="15">
         <v>3046.26</v>
       </c>
     </row>
@@ -3163,10 +3173,10 @@
       <c r="D39" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="15">
         <v>3968.8</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="15">
         <v>3198.66</v>
       </c>
     </row>
@@ -3183,10 +3193,10 @@
       <c r="D40" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="15">
         <v>3968.8</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="15">
         <v>3229.87</v>
       </c>
     </row>
@@ -3203,10 +3213,10 @@
       <c r="D41" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="15">
         <v>3867.57</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="15">
         <v>3194.62</v>
       </c>
     </row>
@@ -3223,10 +3233,10 @@
       <c r="D42" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="15">
         <v>4049.2</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="15">
         <v>3194.62</v>
       </c>
     </row>
@@ -3243,10 +3253,10 @@
       <c r="D43" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="15">
         <v>3991.58</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="15">
         <v>3164.63</v>
       </c>
     </row>
@@ -3263,10 +3273,10 @@
       <c r="D44" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="15">
         <v>3977.5</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="15">
         <v>3142.68</v>
       </c>
     </row>
@@ -3283,10 +3293,10 @@
       <c r="D45" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="15">
         <v>3938.46</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="15">
         <v>3059.92</v>
       </c>
     </row>
@@ -3303,10 +3313,10 @@
       <c r="D46" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="15">
         <v>3945.39</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="15">
         <v>3029.7</v>
       </c>
     </row>
@@ -3323,10 +3333,10 @@
       <c r="D47" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="15">
         <v>3932.44</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="15">
         <v>3019.44</v>
       </c>
     </row>
@@ -3343,10 +3353,10 @@
       <c r="D48" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="15">
         <v>3913.14</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="15">
         <v>3014.54</v>
       </c>
     </row>
@@ -3363,10 +3373,10 @@
       <c r="D49" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="15">
         <v>3913.14</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="15">
         <v>3014.38</v>
       </c>
     </row>
@@ -3383,11 +3393,31 @@
       <c r="D50" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="15">
         <v>3945.05</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="15">
         <v>3014.38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="11">
+        <v>46189</v>
+      </c>
+      <c r="B51" s="11">
+        <v>46189</v>
+      </c>
+      <c r="C51" s="12">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E51" s="15">
+        <v>3974.13</v>
+      </c>
+      <c r="F51" s="15">
+        <v>3015.97</v>
       </c>
     </row>
   </sheetData>
@@ -3400,11 +3430,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3935,7 +3965,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF528F66-5C7C-40F6-B437-A79684695F91}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D38588AE-B2BB-4E3B-8FE7-0F9F6023415E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2AD22E-1607-4AFB-BAA8-88659EA2A368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -415,7 +415,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,6 +465,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -483,13 +491,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -526,10 +535,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -746,6 +757,9 @@
                 <c:pt idx="49">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="50">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -903,6 +917,9 @@
                   <c:v>3945.05</c:v>
                 </c:pt>
                 <c:pt idx="49">
+                  <c:v>3974.13</c:v>
+                </c:pt>
+                <c:pt idx="50">
                   <c:v>3974.13</c:v>
                 </c:pt>
               </c:numCache>
@@ -1097,6 +1114,9 @@
                 <c:pt idx="49">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="50">
+                  <c:v>46196</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1255,6 +1275,9 @@
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>3015.97</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3010.97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2331,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="11.6640625" style="11" customWidth="1"/>
@@ -3418,6 +3441,26 @@
       </c>
       <c r="F51" s="15">
         <v>3015.97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="11">
+        <v>46196</v>
+      </c>
+      <c r="B52" s="11">
+        <v>46196</v>
+      </c>
+      <c r="C52" s="12">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" s="15">
+        <v>3974.13</v>
+      </c>
+      <c r="F52" s="15">
+        <v>3010.97</v>
       </c>
     </row>
   </sheetData>
@@ -3443,14 +3486,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:5" ht="14.4">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="16" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3958,6 +4001,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{143C872D-FFD5-468B-877C-2753837B102E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
